--- a/business_forms/043_september_good_hart_cloth_pre_order_form--business_forms.xlsx
+++ b/business_forms/043_september_good_hart_cloth_pre_order_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>date_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Date 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>time_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Time 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>phone_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Phone 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_one_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Select One</t>
+          <t>Select One 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_multiple_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Select Multiple</t>
+          <t>Select Multiple 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1101,7 +1101,7 @@
   <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1194,7 +1194,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1211,7 +1211,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1228,7 +1228,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_multiple_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1245,7 +1245,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_multiple_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
